--- a/老虎机数学专题-二项分配机率.xlsx
+++ b/老虎机数学专题-二项分配机率.xlsx
@@ -430,7 +430,7 @@
     <t>来源：https://ezslotdesign.com/binomial-distribution/  ｜  对应「说明」页签第 24~27 行  ｜  配合「二项分配 问1+问2+问3」页签</t>
   </si>
   <si>
-    <t>本文函数：BINOM.DIST(k, n, p, 累计?) ／ BINOM.DIST.RANGE(n, p, 下限, 上限)　｜　蓝字＝输入（可直接改），黄底＝关键结果，黑字＝公式</t>
+    <t xml:space="preserve">本文函数：BINOM.DIST(k, n, p, 累计?)（旧式写法 BINOMDIST，本表沿用旧式以与既有页签一致）／ 区间机率 BINOM.DIST.RANGE(n, p, 下限, 上限)，等价写法 = 1 - BINOMDIST(下限-1, n, p, TRUE)　｜　蓝字＝输入（可直接改），黄底＝关键结果</t>
   </si>
   <si>
     <t>公式：P(k) = C(n,k) × p^k × (1-p)^(n-k)，即「n 次独立试验中成功 k 次」的机率。</t>
@@ -487,7 +487,7 @@
     <t>恰好 3 轮出现该图案</t>
   </si>
   <si>
-    <t>BINOM.DIST(k, n, p, FALSE)　（＝问1 的算法）</t>
+    <t xml:space="preserve">BINOM.DIST(k, n, p, FALSE)　（旧式 BINOMDIST，＝问1 的算法）</t>
   </si>
   <si>
     <t>5 轮全出现（k = n）</t>
@@ -499,7 +499,7 @@
     <t>至少 3 轮出现（可连线）</t>
   </si>
   <si>
-    <t>1-BINOM.DIST(k-1, n, p, TRUE)　或　BINOM.DIST.RANGE(n, p, k, n)</t>
+    <t xml:space="preserve">1 - BINOM.DIST(k-1, n, p, TRUE)　或　BINOM.DIST.RANGE(n, p, k, n)　（旧式 BINOMDIST）</t>
   </si>
   <si>
     <t>期望出现轮数 E = n × p</t>
@@ -559,7 +559,7 @@
     <t>坑2：误把 15 格当 15 次独立试验 n = 15</t>
   </si>
   <si>
-    <t>机率虚高约 31 倍，这就是工作簿「问1」提醒的「各图案个数互相牵制」同类陷阱</t>
+    <t xml:space="preserve">机率虚高约 31 倍，这就是工作簿「问1」提醒的「各图案个数互相牵制」同类陷阱</t>
   </si>
   <si>
     <t>坑3：各滚轮带长／p 不同时，要用泊松二项（逐轮相乘），不能用一个 p 概括。</t>
@@ -3485,6 +3485,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:V98" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -8030,6 +8033,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Y101" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -8181,7 +8187,7 @@
         <v>151</v>
       </c>
       <c r="B18" s="10">
-        <f>_xlfn.BINOM.DIST($B$15,$B$13,$B$14,FALSE)</f>
+        <f>BINOMDIST($B$15,$B$13,$B$14,FALSE)</f>
         <v>0.00360966796875</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -8193,7 +8199,7 @@
         <v>153</v>
       </c>
       <c r="B19" s="11">
-        <f>_xlfn.BINOM.DIST($B$13,$B$13,$B$14,FALSE)</f>
+        <f>BINOMDIST($B$13,$B$13,$B$14,FALSE)</f>
         <v>2.373046875e-6</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -8205,7 +8211,7 @@
         <v>155</v>
       </c>
       <c r="B20" s="10">
-        <f>1-_xlfn.BINOM.DIST($B$15-1,$B$13,$B$14,TRUE)</f>
+        <f>1-BINOMDIST($B$15-1,$B$13,$B$14,TRUE)</f>
         <v>0.00375837890624997</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -8311,7 +8317,7 @@
         <v>167</v>
       </c>
       <c r="B32" s="10">
-        <f>1-_xlfn.BINOM.DIST($B$29-1,$B$27,$B$28,TRUE)</f>
+        <f>1-BINOMDIST($B$29-1,$B$27,$B$28,TRUE)</f>
         <v>0.000602214399999967</v>
       </c>
       <c r="C32" s="3" t="s">
@@ -8323,7 +8329,7 @@
         <v>168</v>
       </c>
       <c r="B33" s="11">
-        <f>1-_xlfn.BINOM.DIST(1,$B$27,$B$28,TRUE)</f>
+        <f>1-BINOMDIST(1,$B$27,$B$28,TRUE)</f>
         <v>0.0147579904</v>
       </c>
       <c r="C33" s="3" t="s">
@@ -8364,7 +8370,7 @@
         <v>173</v>
       </c>
       <c r="B38" s="11">
-        <f>1-_xlfn.BINOM.DIST(2,5,0.05,TRUE)</f>
+        <f>1-BINOMDIST(2,5,0.05,TRUE)</f>
         <v>0.00115812500000001</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -8376,7 +8382,7 @@
         <v>175</v>
       </c>
       <c r="B39" s="10">
-        <f>1-_xlfn.BINOM.DIST(2,15,0.05,TRUE)</f>
+        <f>1-BINOMDIST(2,15,0.05,TRUE)</f>
         <v>0.0362002386427291</v>
       </c>
       <c r="C39" s="3" t="s">
@@ -8506,6 +8512,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:C53" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/老虎机数学专题-二项分配机率.xlsx
+++ b/老虎机数学专题-二项分配机率.xlsx
@@ -11,7 +11,7 @@
     <sheet name="二项分配 问1+问2+问3" sheetId="2" r:id="rId2"/>
     <sheet name="二项分配-三句用法" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="196">
   <si>
     <t>二项分配机率（Binomial Distribution）计算模型</t>
   </si>
@@ -623,11 +623,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0%"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -1349,7 +1350,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1479,6 +1480,45 @@
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2276,1178 +2316,1178 @@
       <c r="J16" s="34"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:10">
-      <c r="A17" s="37" t="s">
+      <c r="A17" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
     </row>
     <row r="18" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A18" s="39"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
     </row>
     <row r="22" ht="33" customHeight="1" spans="1:10">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
     </row>
     <row r="24" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A24" s="39"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
+      <c r="A24" s="55"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="38"/>
-      <c r="C26" s="38"/>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A27" s="43" t="s">
+      <c r="A27" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A28" s="43" t="s">
+      <c r="A28" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:10">
-      <c r="A30" s="44" t="s">
+      <c r="A30" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B30" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A31" s="46" t="s">
+      <c r="A31" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="38"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="54"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="38"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="38"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A34" s="46" t="s">
+      <c r="A34" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="63"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
     </row>
     <row r="35" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A35" s="39"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
     </row>
     <row r="37" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A37" s="39"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
+      <c r="A37" s="55"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="43" t="s">
+      <c r="A38" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:10">
-      <c r="A39" s="44" t="s">
+      <c r="A39" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="45" t="s">
+      <c r="C39" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A40" s="46" t="s">
+      <c r="A40" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
-      <c r="J40" s="38"/>
+      <c r="B40" s="69">
+        <v>0.1</v>
+      </c>
+      <c r="C40" s="69">
+        <v>0.15</v>
+      </c>
+      <c r="D40" s="69">
+        <v>0.2</v>
+      </c>
+      <c r="E40" s="69">
+        <v>0.25</v>
+      </c>
+      <c r="F40" s="69">
+        <v>0.3</v>
+      </c>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
     </row>
     <row r="41" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A41" s="39"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
+      <c r="A41" s="55"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="43" t="s">
+      <c r="A42" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
-      <c r="J42" s="38"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
     </row>
     <row r="43" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A43" s="42" t="s">
+      <c r="A43" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="54"/>
     </row>
     <row r="44" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A44" s="39"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="54"/>
     </row>
     <row r="45" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="41"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="54"/>
+      <c r="J46" s="54"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
     </row>
     <row r="48" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="49"/>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
     </row>
     <row r="49" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A49" s="42" t="s">
+      <c r="A49" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
     </row>
     <row r="50" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A50" s="39"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
+      <c r="A50" s="55"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
     </row>
     <row r="51" ht="33" customHeight="1" spans="1:10">
-      <c r="A51" s="41" t="s">
+      <c r="A51" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="41"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="38"/>
-      <c r="I51" s="38"/>
-      <c r="J51" s="38"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="38"/>
+      <c r="B52" s="54"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="54"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="54"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="54"/>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="54"/>
+      <c r="J54" s="54"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="59" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
     </row>
     <row r="56" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A56" s="42" t="s">
+      <c r="A56" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="38"/>
-      <c r="C56" s="38"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
     </row>
     <row r="57" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A57" s="39"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="38"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
-      <c r="J57" s="38"/>
+      <c r="A57" s="55"/>
+      <c r="B57" s="54"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="54"/>
     </row>
     <row r="58" ht="33" customHeight="1" spans="1:10">
-      <c r="A58" s="41" t="s">
+      <c r="A58" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="41"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-      <c r="J58" s="38"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="54"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A59" s="43" t="s">
+      <c r="A59" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="54"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A60" s="41" t="s">
+      <c r="A60" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="41"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="38"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A61" s="43" t="s">
+      <c r="A61" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="38"/>
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="38"/>
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A62" s="43" t="s">
+      <c r="A62" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="38"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54"/>
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
+      <c r="B63" s="54"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="54"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A64" s="43" t="s">
+      <c r="A64" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
+      <c r="B64" s="54"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="54"/>
+      <c r="J64" s="54"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A65" s="43" t="s">
+      <c r="A65" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
+      <c r="B65" s="54"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="54"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="54"/>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:22">
-      <c r="A66" s="50" t="s">
+      <c r="A66" s="66" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A67" s="43" t="s">
+      <c r="A67" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="38"/>
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38"/>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="38"/>
+      <c r="B67" s="54"/>
+      <c r="C67" s="54"/>
+      <c r="D67" s="54"/>
+      <c r="E67" s="54"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="54"/>
+      <c r="H67" s="54"/>
+      <c r="I67" s="54"/>
+      <c r="J67" s="54"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A68" s="43" t="s">
+      <c r="A68" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38"/>
+      <c r="B68" s="54"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="54"/>
+      <c r="I68" s="54"/>
+      <c r="J68" s="54"/>
     </row>
     <row r="69" ht="33" customHeight="1" spans="1:22">
-      <c r="A69" s="41" t="s">
+      <c r="A69" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="38"/>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="54"/>
+      <c r="J69" s="54"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A70" s="43" t="s">
+      <c r="A70" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="38"/>
-      <c r="C70" s="38"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="38"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="38"/>
-      <c r="H70" s="38"/>
-      <c r="I70" s="38"/>
-      <c r="J70" s="38"/>
+      <c r="B70" s="54"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="54"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="54"/>
+      <c r="H70" s="54"/>
+      <c r="I70" s="54"/>
+      <c r="J70" s="54"/>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:22">
-      <c r="A71" s="51" t="s">
+      <c r="A71" s="67" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="72" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A72" s="42" t="s">
+      <c r="A72" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="38"/>
-      <c r="C72" s="38"/>
-      <c r="D72" s="38"/>
-      <c r="E72" s="38"/>
-      <c r="F72" s="38"/>
-      <c r="G72" s="38"/>
-      <c r="H72" s="38"/>
-      <c r="I72" s="38"/>
-      <c r="J72" s="38"/>
+      <c r="B72" s="54"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="54"/>
+      <c r="H72" s="54"/>
+      <c r="I72" s="54"/>
+      <c r="J72" s="54"/>
     </row>
     <row r="73" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A73" s="39"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="38"/>
-      <c r="D73" s="38"/>
-      <c r="E73" s="38"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="38"/>
-      <c r="H73" s="38"/>
-      <c r="I73" s="38"/>
-      <c r="J73" s="38"/>
+      <c r="A73" s="55"/>
+      <c r="B73" s="54"/>
+      <c r="C73" s="54"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="54"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="54"/>
+      <c r="H73" s="54"/>
+      <c r="I73" s="54"/>
+      <c r="J73" s="54"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A74" s="43" t="s">
+      <c r="A74" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="38"/>
-      <c r="C74" s="38"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="38"/>
-      <c r="F74" s="38"/>
-      <c r="G74" s="38"/>
-      <c r="H74" s="38"/>
-      <c r="I74" s="38"/>
-      <c r="J74" s="38"/>
+      <c r="B74" s="54"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="54"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="54"/>
     </row>
     <row r="75" ht="18" customHeight="1" spans="1:22">
-      <c r="A75" s="44" t="s">
+      <c r="A75" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="45" t="s">
+      <c r="B75" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="38"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="38"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
+      <c r="E75" s="54"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="54"/>
+      <c r="H75" s="54"/>
+      <c r="I75" s="54"/>
+      <c r="J75" s="54"/>
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:22">
-      <c r="A76" s="46" t="s">
+      <c r="A76" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="47" t="s">
+      <c r="B76" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C76" s="47"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="38"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="38"/>
-      <c r="H76" s="38"/>
-      <c r="I76" s="38"/>
-      <c r="J76" s="38"/>
+      <c r="C76" s="63"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="54"/>
+      <c r="H76" s="54"/>
+      <c r="I76" s="54"/>
+      <c r="J76" s="54"/>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:22">
-      <c r="A77" s="46" t="s">
+      <c r="A77" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="52" t="s">
+      <c r="B77" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="C77" s="52"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="52"/>
-      <c r="H77" s="52"/>
-      <c r="I77" s="52"/>
-      <c r="J77" s="52"/>
-      <c r="K77" s="52"/>
-      <c r="L77" s="52"/>
-      <c r="M77" s="52"/>
-      <c r="N77" s="52"/>
-      <c r="O77" s="52"/>
-      <c r="P77" s="52"/>
-      <c r="Q77" s="52"/>
-      <c r="R77" s="52"/>
-      <c r="S77" s="52"/>
-      <c r="T77" s="52"/>
-      <c r="U77" s="52"/>
-      <c r="V77" s="52"/>
+      <c r="C77" s="68"/>
+      <c r="D77" s="68"/>
+      <c r="E77" s="68"/>
+      <c r="F77" s="68"/>
+      <c r="G77" s="68"/>
+      <c r="H77" s="68"/>
+      <c r="I77" s="68"/>
+      <c r="J77" s="68"/>
+      <c r="K77" s="68"/>
+      <c r="L77" s="68"/>
+      <c r="M77" s="68"/>
+      <c r="N77" s="68"/>
+      <c r="O77" s="68"/>
+      <c r="P77" s="68"/>
+      <c r="Q77" s="68"/>
+      <c r="R77" s="68"/>
+      <c r="S77" s="68"/>
+      <c r="T77" s="68"/>
+      <c r="U77" s="68"/>
+      <c r="V77" s="68"/>
     </row>
     <row r="78" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A78" s="39"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="38"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="38"/>
-      <c r="H78" s="38"/>
-      <c r="I78" s="38"/>
-      <c r="J78" s="38"/>
+      <c r="A78" s="55"/>
+      <c r="B78" s="54"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="54"/>
+      <c r="I78" s="54"/>
+      <c r="J78" s="54"/>
     </row>
     <row r="79" ht="33" customHeight="1" spans="1:22">
-      <c r="A79" s="41" t="s">
+      <c r="A79" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="B79" s="41"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="38"/>
-      <c r="H79" s="38"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
+      <c r="B79" s="57"/>
+      <c r="C79" s="57"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="54"/>
+      <c r="H79" s="54"/>
+      <c r="I79" s="54"/>
+      <c r="J79" s="54"/>
     </row>
     <row r="80" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A80" s="42" t="s">
+      <c r="A80" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="38"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="38"/>
-      <c r="H80" s="38"/>
-      <c r="I80" s="38"/>
-      <c r="J80" s="38"/>
+      <c r="B80" s="54"/>
+      <c r="C80" s="54"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="54"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="54"/>
+      <c r="H80" s="54"/>
+      <c r="I80" s="54"/>
+      <c r="J80" s="54"/>
     </row>
     <row r="81" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A81" s="39"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="38"/>
-      <c r="I81" s="38"/>
-      <c r="J81" s="38"/>
+      <c r="A81" s="55"/>
+      <c r="B81" s="54"/>
+      <c r="C81" s="54"/>
+      <c r="D81" s="54"/>
+      <c r="E81" s="54"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="54"/>
+      <c r="H81" s="54"/>
+      <c r="I81" s="54"/>
+      <c r="J81" s="54"/>
     </row>
     <row r="82" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A82" s="43" t="s">
+      <c r="A82" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="38"/>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
+      <c r="B82" s="54"/>
+      <c r="C82" s="54"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="54"/>
+      <c r="F82" s="54"/>
+      <c r="G82" s="54"/>
+      <c r="H82" s="54"/>
+      <c r="I82" s="54"/>
+      <c r="J82" s="54"/>
     </row>
     <row r="83" ht="33" customHeight="1" spans="1:10">
-      <c r="A83" s="41" t="s">
+      <c r="A83" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="41"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="38"/>
-      <c r="H83" s="38"/>
-      <c r="I83" s="38"/>
-      <c r="J83" s="38"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="54"/>
+      <c r="F83" s="54"/>
+      <c r="G83" s="54"/>
+      <c r="H83" s="54"/>
+      <c r="I83" s="54"/>
+      <c r="J83" s="54"/>
     </row>
     <row r="84" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A84" s="41" t="s">
+      <c r="A84" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="41"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="41"/>
-      <c r="E84" s="41"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="41"/>
-      <c r="I84" s="41"/>
-      <c r="J84" s="38"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="57"/>
+      <c r="D84" s="57"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="57"/>
+      <c r="G84" s="57"/>
+      <c r="H84" s="57"/>
+      <c r="I84" s="57"/>
+      <c r="J84" s="54"/>
     </row>
     <row r="85" ht="33" customHeight="1" spans="1:10">
-      <c r="A85" s="41" t="s">
+      <c r="A85" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="41"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38"/>
-      <c r="J85" s="38"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="57"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="57"/>
+      <c r="F85" s="57"/>
+      <c r="G85" s="57"/>
+      <c r="H85" s="54"/>
+      <c r="I85" s="54"/>
+      <c r="J85" s="54"/>
     </row>
     <row r="86" ht="33" customHeight="1" spans="1:10">
-      <c r="A86" s="41" t="s">
+      <c r="A86" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="41"/>
-      <c r="C86" s="41"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="38"/>
-      <c r="G86" s="38"/>
-      <c r="H86" s="38"/>
-      <c r="I86" s="38"/>
-      <c r="J86" s="38"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="54"/>
+      <c r="H86" s="54"/>
+      <c r="I86" s="54"/>
+      <c r="J86" s="54"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A87" s="42" t="s">
+      <c r="A87" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="38"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="38"/>
-      <c r="F87" s="38"/>
-      <c r="G87" s="38"/>
-      <c r="H87" s="38"/>
-      <c r="I87" s="38"/>
-      <c r="J87" s="38"/>
+      <c r="B87" s="54"/>
+      <c r="C87" s="54"/>
+      <c r="D87" s="54"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="54"/>
+      <c r="I87" s="54"/>
+      <c r="J87" s="54"/>
     </row>
     <row r="88" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A88" s="39"/>
-      <c r="B88" s="38"/>
-      <c r="C88" s="38"/>
-      <c r="D88" s="38"/>
-      <c r="E88" s="38"/>
-      <c r="F88" s="38"/>
-      <c r="G88" s="38"/>
-      <c r="H88" s="38"/>
-      <c r="I88" s="38"/>
-      <c r="J88" s="38"/>
+      <c r="A88" s="55"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="54"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="54"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="54"/>
+      <c r="I88" s="54"/>
+      <c r="J88" s="54"/>
     </row>
     <row r="89" ht="18" customHeight="1" spans="1:10">
-      <c r="A89" s="44" t="s">
+      <c r="A89" s="60" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="45" t="s">
+      <c r="B89" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C89" s="38"/>
-      <c r="D89" s="38"/>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38"/>
-      <c r="G89" s="38"/>
-      <c r="H89" s="38"/>
-      <c r="I89" s="38"/>
-      <c r="J89" s="38"/>
+      <c r="C89" s="54"/>
+      <c r="D89" s="54"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="54"/>
+      <c r="I89" s="54"/>
+      <c r="J89" s="54"/>
     </row>
     <row r="90" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A90" s="46" t="s">
+      <c r="A90" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="48" t="s">
+      <c r="B90" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="38"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="38"/>
-      <c r="F90" s="38"/>
-      <c r="G90" s="38"/>
-      <c r="H90" s="38"/>
-      <c r="I90" s="38"/>
-      <c r="J90" s="38"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
+      <c r="E90" s="54"/>
+      <c r="F90" s="54"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="54"/>
+      <c r="I90" s="54"/>
+      <c r="J90" s="54"/>
     </row>
     <row r="91" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A91" s="46" t="s">
+      <c r="A91" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="47" t="s">
+      <c r="B91" s="63" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="47"/>
-      <c r="D91" s="38"/>
-      <c r="E91" s="38"/>
-      <c r="F91" s="38"/>
-      <c r="G91" s="38"/>
-      <c r="H91" s="38"/>
-      <c r="I91" s="38"/>
-      <c r="J91" s="38"/>
+      <c r="C91" s="63"/>
+      <c r="D91" s="54"/>
+      <c r="E91" s="54"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="54"/>
+      <c r="I91" s="54"/>
+      <c r="J91" s="54"/>
     </row>
     <row r="92" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A92" s="46" t="s">
+      <c r="A92" s="62" t="s">
         <v>93</v>
       </c>
-      <c r="B92" s="47" t="s">
+      <c r="B92" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="C92" s="47"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="38"/>
-      <c r="F92" s="38"/>
-      <c r="G92" s="38"/>
-      <c r="H92" s="38"/>
-      <c r="I92" s="38"/>
-      <c r="J92" s="38"/>
+      <c r="C92" s="63"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="54"/>
+      <c r="I92" s="54"/>
+      <c r="J92" s="54"/>
     </row>
     <row r="93" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A93" s="46" t="s">
+      <c r="A93" s="62" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="47" t="s">
+      <c r="B93" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="C93" s="47"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="38"/>
-      <c r="F93" s="38"/>
-      <c r="G93" s="38"/>
-      <c r="H93" s="38"/>
-      <c r="I93" s="38"/>
-      <c r="J93" s="38"/>
+      <c r="C93" s="63"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="54"/>
+      <c r="I93" s="54"/>
+      <c r="J93" s="54"/>
     </row>
     <row r="94" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A94" s="46" t="s">
+      <c r="A94" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="B94" s="47" t="s">
+      <c r="B94" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="C94" s="47"/>
-      <c r="D94" s="38"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="38"/>
-      <c r="G94" s="38"/>
-      <c r="H94" s="38"/>
-      <c r="I94" s="38"/>
-      <c r="J94" s="38"/>
+      <c r="C94" s="63"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="54"/>
+      <c r="I94" s="54"/>
+      <c r="J94" s="54"/>
     </row>
     <row r="95" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A95" s="46" t="s">
+      <c r="A95" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="B95" s="47" t="s">
+      <c r="B95" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="C95" s="47"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="38"/>
-      <c r="F95" s="38"/>
-      <c r="G95" s="38"/>
-      <c r="H95" s="38"/>
-      <c r="I95" s="38"/>
-      <c r="J95" s="38"/>
+      <c r="C95" s="63"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="54"/>
+      <c r="I95" s="54"/>
+      <c r="J95" s="54"/>
     </row>
     <row r="96" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A96" s="46" t="s">
+      <c r="A96" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="B96" s="47" t="s">
+      <c r="B96" s="63" t="s">
         <v>102</v>
       </c>
-      <c r="C96" s="47"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="38"/>
-      <c r="F96" s="38"/>
-      <c r="G96" s="38"/>
-      <c r="H96" s="38"/>
-      <c r="I96" s="38"/>
-      <c r="J96" s="38"/>
+      <c r="C96" s="63"/>
+      <c r="D96" s="54"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="54"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="54"/>
+      <c r="I96" s="54"/>
+      <c r="J96" s="54"/>
     </row>
     <row r="97" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A97" s="46" t="s">
+      <c r="A97" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="B97" s="47" t="s">
+      <c r="B97" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="C97" s="47"/>
-      <c r="D97" s="38"/>
-      <c r="E97" s="38"/>
-      <c r="F97" s="38"/>
-      <c r="G97" s="38"/>
-      <c r="H97" s="38"/>
-      <c r="I97" s="38"/>
-      <c r="J97" s="38"/>
+      <c r="C97" s="63"/>
+      <c r="D97" s="54"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="54"/>
+      <c r="G97" s="54"/>
+      <c r="H97" s="54"/>
+      <c r="I97" s="54"/>
+      <c r="J97" s="54"/>
     </row>
     <row r="98" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A98" s="46" t="s">
+      <c r="A98" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="B98" s="47" t="s">
+      <c r="B98" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="C98" s="47"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="38"/>
-      <c r="F98" s="38"/>
-      <c r="G98" s="38"/>
-      <c r="H98" s="38"/>
-      <c r="I98" s="38"/>
-      <c r="J98" s="38"/>
+      <c r="C98" s="63"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="54"/>
+      <c r="I98" s="54"/>
+      <c r="J98" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -4680,23 +4720,23 @@
         <v>0</v>
       </c>
       <c r="N30" s="26">
-        <f t="shared" ref="N30:N35" si="5">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(N$29,$B$29:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(N$29,$B$29:$D$35,3,FALSE()),TRUE()))</f>
+        <f t="shared" ref="N30:N35" si="5">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(N$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(N$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.987279516358749</v>
       </c>
       <c r="O30" s="26">
-        <f t="shared" ref="O30:O35" si="6">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(O$29,$B$29:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(O$29,$B$29:$D$35,3,FALSE()),TRUE()))</f>
+        <f t="shared" ref="O30:O35" si="6">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(O$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(O$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.93829461326294</v>
       </c>
       <c r="P30" s="26">
-        <f t="shared" ref="P30:P35" si="7">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(P$29,$B$29:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(P$29,$B$29:$D$35,3,FALSE()),TRUE()))</f>
+        <f t="shared" ref="P30:P35" si="7">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(P$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(P$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.835766276063232</v>
       </c>
       <c r="Q30" s="26">
-        <f t="shared" ref="Q30:Q35" si="8">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(Q$29,$B$29:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(Q$29,$B$29:$D$35,3,FALSE()),TRUE()))</f>
+        <f t="shared" ref="Q30:Q35" si="8">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(Q$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(Q$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.686485941521823</v>
       </c>
       <c r="R30" s="26">
-        <f t="shared" ref="R30:R35" si="9">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(R$29,$B$29:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(R$29,$B$29:$D$35,3,FALSE()),TRUE()))</f>
+        <f t="shared" ref="R30:R35" si="9">BINOMDIST(IF($M30=15,15,$M31-1),$F$45,VLOOKUP(R$29,$B$30:$D$35,3,FALSE()),TRUE())-IF($M30&lt;=0,0,BINOMDIST($M30-1,$F$45,VLOOKUP(R$29,$B$30:$D$35,3,FALSE()),TRUE()))</f>
         <v>0.515491059226843</v>
       </c>
       <c r="S30" s="16"/>
@@ -5790,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="20">
-        <f t="shared" ref="I63:Y63" si="10">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I63:Y63" si="10">IFERROR(BINOMDIST($H63-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.205891132094649</v>
       </c>
       <c r="J63" s="20" t="str">
@@ -5876,7 +5916,7 @@
         <v>1</v>
       </c>
       <c r="I64" s="20">
-        <f t="shared" ref="I64:Y64" si="11">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I64:Y64" si="11">IFERROR(BINOMDIST($H64-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.343151886824415</v>
       </c>
       <c r="J64" s="20">
@@ -5962,7 +6002,7 @@
         <v>2</v>
       </c>
       <c r="I65" s="20">
-        <f t="shared" ref="I65:Y65" si="12">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I65:Y65" si="12">IFERROR(BINOMDIST($H65-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.266895911974545</v>
       </c>
       <c r="J65" s="20">
@@ -6048,7 +6088,7 @@
         <v>3</v>
       </c>
       <c r="I66" s="20">
-        <f t="shared" ref="I66:Y66" si="13">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I66:Y66" si="13">IFERROR(BINOMDIST($H66-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.128505439098855</v>
       </c>
       <c r="J66" s="20">
@@ -6134,7 +6174,7 @@
         <v>4</v>
       </c>
       <c r="I67" s="20">
-        <f t="shared" ref="I67:Y67" si="14">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I67:Y67" si="14">IFERROR(BINOMDIST($H67-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.0428351463662851</v>
       </c>
       <c r="J67" s="20">
@@ -6218,7 +6258,7 @@
         <v>5</v>
       </c>
       <c r="I68" s="28">
-        <f t="shared" ref="I68:Y68" si="15">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I68:Y68" si="15">IFERROR(BINOMDIST($H68-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.010470813556203</v>
       </c>
       <c r="J68" s="28">
@@ -6298,7 +6338,7 @@
         <v>6</v>
       </c>
       <c r="I69" s="20">
-        <f t="shared" ref="I69:Y69" si="16">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I69:Y69" si="16">IFERROR(BINOMDIST($H69-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.001939039547445</v>
       </c>
       <c r="J69" s="20">
@@ -6378,7 +6418,7 @@
         <v>7</v>
       </c>
       <c r="I70" s="20">
-        <f t="shared" ref="I70:Y70" si="17">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I70:Y70" si="17">IFERROR(BINOMDIST($H70-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>0.000277005649635</v>
       </c>
       <c r="J70" s="20">
@@ -6458,7 +6498,7 @@
         <v>8</v>
       </c>
       <c r="I71" s="20">
-        <f t="shared" ref="I71:Y71" si="18">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I71:Y71" si="18">IFERROR(BINOMDIST($H71-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.0778405515e-5</v>
       </c>
       <c r="J71" s="20">
@@ -6538,7 +6578,7 @@
         <v>9</v>
       </c>
       <c r="I72" s="20">
-        <f t="shared" ref="I72:Y72" si="19">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I72:Y72" si="19">IFERROR(BINOMDIST($H72-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>2.659862205e-6</v>
       </c>
       <c r="J72" s="20">
@@ -6618,7 +6658,7 @@
         <v>10</v>
       </c>
       <c r="I73" s="20">
-        <f t="shared" ref="I73:Y73" si="20">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I73:Y73" si="20">IFERROR(BINOMDIST($H73-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.77324147e-7</v>
       </c>
       <c r="J73" s="20">
@@ -6698,7 +6738,7 @@
         <v>11</v>
       </c>
       <c r="I74" s="20">
-        <f t="shared" ref="I74:Y74" si="21">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I74:Y74" si="21">IFERROR(BINOMDIST($H74-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.95576499999999e-9</v>
       </c>
       <c r="J74" s="20">
@@ -6778,7 +6818,7 @@
         <v>12</v>
       </c>
       <c r="I75" s="20">
-        <f t="shared" ref="I75:Y75" si="22">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I75:Y75" si="22">IFERROR(BINOMDIST($H75-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>3.31695000000002e-10</v>
       </c>
       <c r="J75" s="20">
@@ -6858,7 +6898,7 @@
         <v>13</v>
       </c>
       <c r="I76" s="20">
-        <f t="shared" ref="I76:Y76" si="23">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I76:Y76" si="23">IFERROR(BINOMDIST($H76-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>8.50500000000002e-12</v>
       </c>
       <c r="J76" s="20">
@@ -6938,7 +6978,7 @@
         <v>14</v>
       </c>
       <c r="I77" s="20">
-        <f t="shared" ref="I77:Y77" si="24">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I77:Y77" si="24">IFERROR(BINOMDIST($H77-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1.35e-13</v>
       </c>
       <c r="J77" s="20">
@@ -7018,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="I78" s="20">
-        <f t="shared" ref="I78:Y78" si="25">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$62:$D$68,3,FALSE()),FALSE()),"")</f>
+        <f t="shared" ref="I78:Y78" si="25">IFERROR(BINOMDIST($H78-I$62,15-I$62,VLOOKUP($F$63,$B$63:$D$68,3,FALSE()),FALSE()),"")</f>
         <v>1e-15</v>
       </c>
       <c r="J78" s="20">

--- a/老虎机数学专题-二项分配机率.xlsx
+++ b/老虎机数学专题-二项分配机率.xlsx
@@ -11,7 +11,7 @@
     <sheet name="二项分配 问1+问2+问3" sheetId="2" r:id="rId2"/>
     <sheet name="二项分配-三句用法" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="191">
   <si>
     <t>二项分配机率（Binomial Distribution）计算模型</t>
   </si>
@@ -151,21 +151,6 @@
     <t>Chance</t>
   </si>
   <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
     <t>（五图机率合计 100%）</t>
   </si>
   <si>
@@ -430,7 +415,7 @@
     <t>来源：https://ezslotdesign.com/binomial-distribution/  ｜  对应「说明」页签第 24~27 行  ｜  配合「二项分配 问1+问2+问3」页签</t>
   </si>
   <si>
-    <t xml:space="preserve">本文函数：BINOM.DIST(k, n, p, 累计?)（旧式写法 BINOMDIST，本表沿用旧式以与既有页签一致）／ 区间机率 BINOM.DIST.RANGE(n, p, 下限, 上限)，等价写法 = 1 - BINOMDIST(下限-1, n, p, TRUE)　｜　蓝字＝输入（可直接改），黄底＝关键结果</t>
+    <t>本文函数：BINOM.DIST(k, n, p, 累计?)（旧式写法 BINOMDIST，本表沿用旧式以与既有页签一致）／ 区间机率 BINOM.DIST.RANGE(n, p, 下限, 上限)，等价写法 = 1 - BINOMDIST(下限-1, n, p, TRUE)　｜　蓝字＝输入（可直接改），黄底＝关键结果</t>
   </si>
   <si>
     <t>公式：P(k) = C(n,k) × p^k × (1-p)^(n-k)，即「n 次独立试验中成功 k 次」的机率。</t>
@@ -487,7 +472,7 @@
     <t>恰好 3 轮出现该图案</t>
   </si>
   <si>
-    <t xml:space="preserve">BINOM.DIST(k, n, p, FALSE)　（旧式 BINOMDIST，＝问1 的算法）</t>
+    <t>BINOM.DIST(k, n, p, FALSE)　（旧式 BINOMDIST，＝问1 的算法）</t>
   </si>
   <si>
     <t>5 轮全出现（k = n）</t>
@@ -499,7 +484,7 @@
     <t>至少 3 轮出现（可连线）</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - BINOM.DIST(k-1, n, p, TRUE)　或　BINOM.DIST.RANGE(n, p, k, n)　（旧式 BINOMDIST）</t>
+    <t>1 - BINOM.DIST(k-1, n, p, TRUE)　或　BINOM.DIST.RANGE(n, p, k, n)　（旧式 BINOMDIST）</t>
   </si>
   <si>
     <t>期望出现轮数 E = n × p</t>
@@ -559,7 +544,7 @@
     <t>坑2：误把 15 格当 15 次独立试验 n = 15</t>
   </si>
   <si>
-    <t xml:space="preserve">机率虚高约 31 倍，这就是工作簿「问1」提醒的「各图案个数互相牵制」同类陷阱</t>
+    <t>机率虚高约 31 倍，这就是工作簿「问1」提醒的「各图案个数互相牵制」同类陷阱</t>
   </si>
   <si>
     <t>坑3：各滚轮带长／p 不同时，要用泊松二项（逐轮相乘），不能用一个 p 概括。</t>
@@ -623,14 +608,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0%"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -713,13 +697,6 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1205,152 +1182,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1442,44 +1419,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1509,7 +1448,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1518,7 +1457,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1768,7 +1707,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9819640" y="244475"/>
-          <a:ext cx="5717540" cy="1993900"/>
+          <a:ext cx="5717540" cy="2209800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2316,1178 +2255,1178 @@
       <c r="J16" s="34"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:10">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
     </row>
     <row r="18" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A18" s="55"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="54"/>
-      <c r="J18" s="54"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="54"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="54"/>
-      <c r="J19" s="54"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A20" s="56" t="s">
+      <c r="A20" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="54"/>
-      <c r="J20" s="54"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A21" s="56" t="s">
+      <c r="A21" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
     </row>
     <row r="22" ht="33" customHeight="1" spans="1:10">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A23" s="58" t="s">
+      <c r="A23" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
     </row>
     <row r="24" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A24" s="55"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="54"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="54"/>
-      <c r="J25" s="54"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="54"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A29" s="59" t="s">
+      <c r="A29" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="54"/>
-      <c r="C29" s="54"/>
-      <c r="D29" s="54"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-      <c r="J29" s="54"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:10">
-      <c r="A30" s="60" t="s">
+      <c r="A30" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="54"/>
-      <c r="J30" s="54"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
     </row>
     <row r="31" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="54"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="38"/>
     </row>
     <row r="32" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-      <c r="I32" s="54"/>
-      <c r="J32" s="54"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
     </row>
     <row r="33" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A33" s="62" t="s">
+      <c r="A33" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="54"/>
-      <c r="J33" s="54"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
     </row>
     <row r="34" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A34" s="62" t="s">
+      <c r="A34" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="63"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="63"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="63"/>
-      <c r="I34" s="54"/>
-      <c r="J34" s="54"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
     </row>
     <row r="35" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A35" s="55"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A36" s="58" t="s">
+      <c r="A36" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="54"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
     </row>
     <row r="37" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A37" s="55"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="54"/>
+      <c r="A37" s="39"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A38" s="59" t="s">
+      <c r="A38" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:10">
-      <c r="A39" s="60" t="s">
+      <c r="A39" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="61" t="s">
+      <c r="B39" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="61" t="s">
+      <c r="D39" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="61" t="s">
+      <c r="E39" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="61" t="s">
+      <c r="F39" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="54"/>
-      <c r="J39" s="54"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="69">
+      <c r="B40" s="48">
         <v>0.1</v>
       </c>
-      <c r="C40" s="69">
+      <c r="C40" s="48">
         <v>0.15</v>
       </c>
-      <c r="D40" s="69">
+      <c r="D40" s="48">
         <v>0.2</v>
       </c>
-      <c r="E40" s="69">
+      <c r="E40" s="48">
         <v>0.25</v>
       </c>
-      <c r="F40" s="69">
+      <c r="F40" s="48">
         <v>0.3</v>
       </c>
-      <c r="G40" s="54"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="54"/>
-      <c r="J40" s="54"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
     </row>
     <row r="41" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A41" s="55"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="54"/>
-      <c r="I41" s="54"/>
-      <c r="J41" s="54"/>
+      <c r="A41" s="39"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A42" s="59" t="s">
+      <c r="A42" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
+    </row>
+    <row r="43" ht="19.5" customHeight="1" spans="1:10">
+      <c r="A43" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+    </row>
+    <row r="44" ht="13.5" customHeight="1" spans="1:10">
+      <c r="A44" s="39"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+    </row>
+    <row r="45" ht="33" customHeight="1" spans="1:10">
+      <c r="A45" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A46" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="38"/>
+    </row>
+    <row r="47" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A47" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
+    </row>
+    <row r="48" ht="49.5" customHeight="1" spans="1:10">
+      <c r="A48" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="54"/>
-      <c r="J42" s="54"/>
-    </row>
-    <row r="43" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A43" s="58" t="s">
+      <c r="B48" s="49"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49"/>
+    </row>
+    <row r="49" ht="19.5" customHeight="1" spans="1:10">
+      <c r="A49" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="54"/>
-      <c r="C43" s="54"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="54"/>
-      <c r="J43" s="54"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A44" s="55"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="54"/>
-      <c r="E44" s="54"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="54"/>
-      <c r="J44" s="54"/>
-    </row>
-    <row r="45" ht="33" customHeight="1" spans="1:10">
-      <c r="A45" s="57" t="s">
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="38"/>
+    </row>
+    <row r="50" ht="13.5" customHeight="1" spans="1:10">
+      <c r="A50" s="39"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
+    </row>
+    <row r="51" ht="33" customHeight="1" spans="1:10">
+      <c r="A51" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="57"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="54"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A46" s="59" t="s">
+      <c r="B51" s="41"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="41"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="38"/>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A52" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="54"/>
-      <c r="C46" s="54"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="54"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="54"/>
-      <c r="H46" s="54"/>
-      <c r="I46" s="54"/>
-      <c r="J46" s="54"/>
-    </row>
-    <row r="47" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A47" s="59" t="s">
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+    </row>
+    <row r="53" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A53" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="54"/>
-      <c r="H47" s="54"/>
-      <c r="I47" s="54"/>
-      <c r="J47" s="54"/>
-    </row>
-    <row r="48" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A48" s="65" t="s">
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+    </row>
+    <row r="54" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A54" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="65"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="65"/>
-    </row>
-    <row r="49" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A49" s="58" t="s">
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+    </row>
+    <row r="55" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A55" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A50" s="55"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="54"/>
-      <c r="J50" s="54"/>
-    </row>
-    <row r="51" ht="33" customHeight="1" spans="1:10">
-      <c r="A51" s="57" t="s">
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1" spans="1:10">
+      <c r="A56" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="54"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="54"/>
-      <c r="J51" s="54"/>
-    </row>
-    <row r="52" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A52" s="59" t="s">
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+    </row>
+    <row r="57" ht="13.5" customHeight="1" spans="1:10">
+      <c r="A57" s="39"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+    </row>
+    <row r="58" ht="33" customHeight="1" spans="1:10">
+      <c r="A58" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="54"/>
-      <c r="I52" s="54"/>
-      <c r="J52" s="54"/>
-    </row>
-    <row r="53" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A53" s="59" t="s">
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+    </row>
+    <row r="59" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A59" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="54"/>
-      <c r="H53" s="54"/>
-      <c r="I53" s="54"/>
-      <c r="J53" s="54"/>
-    </row>
-    <row r="54" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A54" s="59" t="s">
+      <c r="B59" s="38"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38"/>
+    </row>
+    <row r="60" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A60" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="54"/>
-      <c r="C54" s="54"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="54"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="54"/>
-      <c r="I54" s="54"/>
-      <c r="J54" s="54"/>
-    </row>
-    <row r="55" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A55" s="59" t="s">
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+    </row>
+    <row r="61" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A61" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="54"/>
-      <c r="C55" s="54"/>
-      <c r="D55" s="54"/>
-      <c r="E55" s="54"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="54"/>
-      <c r="H55" s="54"/>
-      <c r="I55" s="54"/>
-      <c r="J55" s="54"/>
-    </row>
-    <row r="56" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A56" s="58" t="s">
+      <c r="B61" s="38"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+    </row>
+    <row r="62" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A62" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="54"/>
-      <c r="C56" s="54"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="54"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-    </row>
-    <row r="57" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A57" s="55"/>
-      <c r="B57" s="54"/>
-      <c r="C57" s="54"/>
-      <c r="D57" s="54"/>
-      <c r="E57" s="54"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="54"/>
-      <c r="H57" s="54"/>
-      <c r="I57" s="54"/>
-      <c r="J57" s="54"/>
-    </row>
-    <row r="58" ht="33" customHeight="1" spans="1:10">
-      <c r="A58" s="57" t="s">
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+    </row>
+    <row r="63" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A63" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="57"/>
-      <c r="C58" s="57"/>
-      <c r="D58" s="57"/>
-      <c r="E58" s="57"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="54"/>
-      <c r="I58" s="54"/>
-      <c r="J58" s="54"/>
-    </row>
-    <row r="59" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A59" s="59" t="s">
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+    </row>
+    <row r="64" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A64" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
-      <c r="D59" s="54"/>
-      <c r="E59" s="54"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="54"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="54"/>
-    </row>
-    <row r="60" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A60" s="57" t="s">
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+    </row>
+    <row r="65" ht="16.5" customHeight="1" spans="1:22">
+      <c r="A65" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="B60" s="57"/>
-      <c r="C60" s="57"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="54"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="54"/>
-    </row>
-    <row r="61" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A61" s="59" t="s">
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:22">
+      <c r="A66" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
-      <c r="H61" s="54"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="54"/>
-    </row>
-    <row r="62" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A62" s="59" t="s">
+    </row>
+    <row r="67" ht="16.5" customHeight="1" spans="1:22">
+      <c r="A67" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="54"/>
-      <c r="C62" s="54"/>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="54"/>
-      <c r="H62" s="54"/>
-      <c r="I62" s="54"/>
-      <c r="J62" s="54"/>
-    </row>
-    <row r="63" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A63" s="59" t="s">
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="38"/>
+    </row>
+    <row r="68" ht="16.5" customHeight="1" spans="1:22">
+      <c r="A68" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="54"/>
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="G63" s="54"/>
-      <c r="H63" s="54"/>
-      <c r="I63" s="54"/>
-      <c r="J63" s="54"/>
-    </row>
-    <row r="64" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A64" s="59" t="s">
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+    </row>
+    <row r="69" ht="33" customHeight="1" spans="1:22">
+      <c r="A69" s="41" t="s">
         <v>64</v>
       </c>
-      <c r="B64" s="54"/>
-      <c r="C64" s="54"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="54"/>
-      <c r="H64" s="54"/>
-      <c r="I64" s="54"/>
-      <c r="J64" s="54"/>
-    </row>
-    <row r="65" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A65" s="59" t="s">
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+    </row>
+    <row r="70" ht="16.5" customHeight="1" spans="1:22">
+      <c r="A70" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="B65" s="54"/>
-      <c r="C65" s="54"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="54"/>
-      <c r="H65" s="54"/>
-      <c r="I65" s="54"/>
-      <c r="J65" s="54"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="1:22">
-      <c r="A66" s="66" t="s">
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="1:22">
+      <c r="A71" s="51" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A67" s="59" t="s">
+    <row r="72" ht="19.5" customHeight="1" spans="1:22">
+      <c r="A72" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B67" s="54"/>
-      <c r="C67" s="54"/>
-      <c r="D67" s="54"/>
-      <c r="E67" s="54"/>
-      <c r="F67" s="54"/>
-      <c r="G67" s="54"/>
-      <c r="H67" s="54"/>
-      <c r="I67" s="54"/>
-      <c r="J67" s="54"/>
-    </row>
-    <row r="68" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A68" s="59" t="s">
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+    </row>
+    <row r="73" ht="13.5" customHeight="1" spans="1:22">
+      <c r="A73" s="39"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" spans="1:22">
+      <c r="A74" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="54"/>
-      <c r="C68" s="54"/>
-      <c r="D68" s="54"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="54"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-    </row>
-    <row r="69" ht="33" customHeight="1" spans="1:22">
-      <c r="A69" s="57" t="s">
+      <c r="B74" s="38"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+    </row>
+    <row r="75" ht="18" customHeight="1" spans="1:22">
+      <c r="A75" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="B69" s="57"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="57"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="54"/>
-      <c r="H69" s="54"/>
-      <c r="I69" s="54"/>
-      <c r="J69" s="54"/>
-    </row>
-    <row r="70" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A70" s="59" t="s">
+      <c r="B75" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="B70" s="54"/>
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="54"/>
-      <c r="G70" s="54"/>
-      <c r="H70" s="54"/>
-      <c r="I70" s="54"/>
-      <c r="J70" s="54"/>
-    </row>
-    <row r="71" ht="15" customHeight="1" spans="1:22">
-      <c r="A71" s="67" t="s">
+      <c r="C75" s="38"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="38"/>
+      <c r="J75" s="38"/>
+    </row>
+    <row r="76" ht="14.25" customHeight="1" spans="1:22">
+      <c r="A76" s="46" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="72" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A72" s="58" t="s">
+      <c r="B76" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="54"/>
-      <c r="C72" s="54"/>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
-      <c r="F72" s="54"/>
-      <c r="G72" s="54"/>
-      <c r="H72" s="54"/>
-      <c r="I72" s="54"/>
-      <c r="J72" s="54"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A73" s="55"/>
-      <c r="B73" s="54"/>
-      <c r="C73" s="54"/>
-      <c r="D73" s="54"/>
-      <c r="E73" s="54"/>
-      <c r="F73" s="54"/>
-      <c r="G73" s="54"/>
-      <c r="H73" s="54"/>
-      <c r="I73" s="54"/>
-      <c r="J73" s="54"/>
-    </row>
-    <row r="74" ht="16.5" customHeight="1" spans="1:22">
-      <c r="A74" s="59" t="s">
+      <c r="C76" s="47"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="38"/>
+      <c r="J76" s="38"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" spans="1:22">
+      <c r="A77" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="54"/>
-      <c r="C74" s="54"/>
-      <c r="D74" s="54"/>
-      <c r="E74" s="54"/>
-      <c r="F74" s="54"/>
-      <c r="G74" s="54"/>
-      <c r="H74" s="54"/>
-      <c r="I74" s="54"/>
-      <c r="J74" s="54"/>
-    </row>
-    <row r="75" ht="18" customHeight="1" spans="1:22">
-      <c r="A75" s="60" t="s">
+      <c r="B77" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="61" t="s">
+      <c r="C77" s="52"/>
+      <c r="D77" s="52"/>
+      <c r="E77" s="52"/>
+      <c r="F77" s="52"/>
+      <c r="G77" s="52"/>
+      <c r="H77" s="52"/>
+      <c r="I77" s="52"/>
+      <c r="J77" s="52"/>
+      <c r="K77" s="52"/>
+      <c r="L77" s="52"/>
+      <c r="M77" s="52"/>
+      <c r="N77" s="52"/>
+      <c r="O77" s="52"/>
+      <c r="P77" s="52"/>
+      <c r="Q77" s="52"/>
+      <c r="R77" s="52"/>
+      <c r="S77" s="52"/>
+      <c r="T77" s="52"/>
+      <c r="U77" s="52"/>
+      <c r="V77" s="52"/>
+    </row>
+    <row r="78" ht="13.5" customHeight="1" spans="1:22">
+      <c r="A78" s="39"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="38"/>
+      <c r="J78" s="38"/>
+    </row>
+    <row r="79" ht="33" customHeight="1" spans="1:22">
+      <c r="A79" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="54"/>
-      <c r="D75" s="54"/>
-      <c r="E75" s="54"/>
-      <c r="F75" s="54"/>
-      <c r="G75" s="54"/>
-      <c r="H75" s="54"/>
-      <c r="I75" s="54"/>
-      <c r="J75" s="54"/>
-    </row>
-    <row r="76" ht="14.25" customHeight="1" spans="1:22">
-      <c r="A76" s="62" t="s">
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1" spans="1:22">
+      <c r="A80" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="B76" s="63" t="s">
+      <c r="B80" s="38"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="38"/>
+      <c r="J80" s="38"/>
+    </row>
+    <row r="81" ht="13.5" customHeight="1" spans="1:10">
+      <c r="A81" s="39"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+    </row>
+    <row r="82" ht="16.5" customHeight="1" spans="1:10">
+      <c r="A82" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="C76" s="63"/>
-      <c r="D76" s="54"/>
-      <c r="E76" s="54"/>
-      <c r="F76" s="54"/>
-      <c r="G76" s="54"/>
-      <c r="H76" s="54"/>
-      <c r="I76" s="54"/>
-      <c r="J76" s="54"/>
-    </row>
-    <row r="77" ht="15" customHeight="1" spans="1:22">
-      <c r="A77" s="62" t="s">
+      <c r="B82" s="38"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+    </row>
+    <row r="83" ht="33" customHeight="1" spans="1:10">
+      <c r="A83" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="68" t="s">
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="38"/>
+      <c r="J83" s="38"/>
+    </row>
+    <row r="84" ht="49.5" customHeight="1" spans="1:10">
+      <c r="A84" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C77" s="68"/>
-      <c r="D77" s="68"/>
-      <c r="E77" s="68"/>
-      <c r="F77" s="68"/>
-      <c r="G77" s="68"/>
-      <c r="H77" s="68"/>
-      <c r="I77" s="68"/>
-      <c r="J77" s="68"/>
-      <c r="K77" s="68"/>
-      <c r="L77" s="68"/>
-      <c r="M77" s="68"/>
-      <c r="N77" s="68"/>
-      <c r="O77" s="68"/>
-      <c r="P77" s="68"/>
-      <c r="Q77" s="68"/>
-      <c r="R77" s="68"/>
-      <c r="S77" s="68"/>
-      <c r="T77" s="68"/>
-      <c r="U77" s="68"/>
-      <c r="V77" s="68"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1" spans="1:22">
-      <c r="A78" s="55"/>
-      <c r="B78" s="54"/>
-      <c r="C78" s="54"/>
-      <c r="D78" s="54"/>
-      <c r="E78" s="54"/>
-      <c r="F78" s="54"/>
-      <c r="G78" s="54"/>
-      <c r="H78" s="54"/>
-      <c r="I78" s="54"/>
-      <c r="J78" s="54"/>
-    </row>
-    <row r="79" ht="33" customHeight="1" spans="1:22">
-      <c r="A79" s="57" t="s">
+      <c r="B84" s="41"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="41"/>
+      <c r="F84" s="41"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41"/>
+      <c r="I84" s="41"/>
+      <c r="J84" s="38"/>
+    </row>
+    <row r="85" ht="33" customHeight="1" spans="1:10">
+      <c r="A85" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B79" s="57"/>
-      <c r="C79" s="57"/>
-      <c r="D79" s="57"/>
-      <c r="E79" s="57"/>
-      <c r="F79" s="54"/>
-      <c r="G79" s="54"/>
-      <c r="H79" s="54"/>
-      <c r="I79" s="54"/>
-      <c r="J79" s="54"/>
-    </row>
-    <row r="80" ht="19.5" customHeight="1" spans="1:22">
-      <c r="A80" s="58" t="s">
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="41"/>
+      <c r="F85" s="41"/>
+      <c r="G85" s="41"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
+      <c r="J85" s="38"/>
+    </row>
+    <row r="86" ht="33" customHeight="1" spans="1:10">
+      <c r="A86" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="54"/>
-      <c r="C80" s="54"/>
-      <c r="D80" s="54"/>
-      <c r="E80" s="54"/>
-      <c r="F80" s="54"/>
-      <c r="G80" s="54"/>
-      <c r="H80" s="54"/>
-      <c r="I80" s="54"/>
-      <c r="J80" s="54"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A81" s="55"/>
-      <c r="B81" s="54"/>
-      <c r="C81" s="54"/>
-      <c r="D81" s="54"/>
-      <c r="E81" s="54"/>
-      <c r="F81" s="54"/>
-      <c r="G81" s="54"/>
-      <c r="H81" s="54"/>
-      <c r="I81" s="54"/>
-      <c r="J81" s="54"/>
-    </row>
-    <row r="82" ht="16.5" customHeight="1" spans="1:10">
-      <c r="A82" s="59" t="s">
+      <c r="B86" s="41"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="38"/>
+      <c r="G86" s="38"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+      <c r="J86" s="38"/>
+    </row>
+    <row r="87" ht="19.5" customHeight="1" spans="1:10">
+      <c r="A87" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="B82" s="54"/>
-      <c r="C82" s="54"/>
-      <c r="D82" s="54"/>
-      <c r="E82" s="54"/>
-      <c r="F82" s="54"/>
-      <c r="G82" s="54"/>
-      <c r="H82" s="54"/>
-      <c r="I82" s="54"/>
-      <c r="J82" s="54"/>
-    </row>
-    <row r="83" ht="33" customHeight="1" spans="1:10">
-      <c r="A83" s="57" t="s">
+      <c r="B87" s="38"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38"/>
+      <c r="G87" s="38"/>
+      <c r="H87" s="38"/>
+      <c r="I87" s="38"/>
+      <c r="J87" s="38"/>
+    </row>
+    <row r="88" ht="13.5" customHeight="1" spans="1:10">
+      <c r="A88" s="39"/>
+      <c r="B88" s="38"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38"/>
+      <c r="G88" s="38"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="38"/>
+      <c r="J88" s="38"/>
+    </row>
+    <row r="89" ht="18" customHeight="1" spans="1:10">
+      <c r="A89" s="44" t="s">
         <v>83</v>
       </c>
-      <c r="B83" s="57"/>
-      <c r="C83" s="57"/>
-      <c r="D83" s="57"/>
-      <c r="E83" s="54"/>
-      <c r="F83" s="54"/>
-      <c r="G83" s="54"/>
-      <c r="H83" s="54"/>
-      <c r="I83" s="54"/>
-      <c r="J83" s="54"/>
-    </row>
-    <row r="84" ht="49.5" customHeight="1" spans="1:10">
-      <c r="A84" s="57" t="s">
+      <c r="B89" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38"/>
+      <c r="G89" s="38"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="38"/>
+      <c r="J89" s="38"/>
+    </row>
+    <row r="90" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A90" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B84" s="57"/>
-      <c r="C84" s="57"/>
-      <c r="D84" s="57"/>
-      <c r="E84" s="57"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="57"/>
-      <c r="H84" s="57"/>
-      <c r="I84" s="57"/>
-      <c r="J84" s="54"/>
-    </row>
-    <row r="85" ht="33" customHeight="1" spans="1:10">
-      <c r="A85" s="57" t="s">
+      <c r="B90" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="57"/>
-      <c r="C85" s="57"/>
-      <c r="D85" s="57"/>
-      <c r="E85" s="57"/>
-      <c r="F85" s="57"/>
-      <c r="G85" s="57"/>
-      <c r="H85" s="54"/>
-      <c r="I85" s="54"/>
-      <c r="J85" s="54"/>
-    </row>
-    <row r="86" ht="33" customHeight="1" spans="1:10">
-      <c r="A86" s="57" t="s">
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="38"/>
+      <c r="F90" s="38"/>
+      <c r="G90" s="38"/>
+      <c r="H90" s="38"/>
+      <c r="I90" s="38"/>
+      <c r="J90" s="38"/>
+    </row>
+    <row r="91" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A91" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="B86" s="57"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="54"/>
-      <c r="F86" s="54"/>
-      <c r="G86" s="54"/>
-      <c r="H86" s="54"/>
-      <c r="I86" s="54"/>
-      <c r="J86" s="54"/>
-    </row>
-    <row r="87" ht="19.5" customHeight="1" spans="1:10">
-      <c r="A87" s="58" t="s">
+      <c r="B91" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="B87" s="54"/>
-      <c r="C87" s="54"/>
-      <c r="D87" s="54"/>
-      <c r="E87" s="54"/>
-      <c r="F87" s="54"/>
-      <c r="G87" s="54"/>
-      <c r="H87" s="54"/>
-      <c r="I87" s="54"/>
-      <c r="J87" s="54"/>
-    </row>
-    <row r="88" ht="13.5" customHeight="1" spans="1:10">
-      <c r="A88" s="55"/>
-      <c r="B88" s="54"/>
-      <c r="C88" s="54"/>
-      <c r="D88" s="54"/>
-      <c r="E88" s="54"/>
-      <c r="F88" s="54"/>
-      <c r="G88" s="54"/>
-      <c r="H88" s="54"/>
-      <c r="I88" s="54"/>
-      <c r="J88" s="54"/>
-    </row>
-    <row r="89" ht="18" customHeight="1" spans="1:10">
-      <c r="A89" s="60" t="s">
+      <c r="C91" s="47"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="38"/>
+      <c r="F91" s="38"/>
+      <c r="G91" s="38"/>
+      <c r="H91" s="38"/>
+      <c r="I91" s="38"/>
+      <c r="J91" s="38"/>
+    </row>
+    <row r="92" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A92" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C89" s="54"/>
-      <c r="D89" s="54"/>
-      <c r="E89" s="54"/>
-      <c r="F89" s="54"/>
-      <c r="G89" s="54"/>
-      <c r="H89" s="54"/>
-      <c r="I89" s="54"/>
-      <c r="J89" s="54"/>
-    </row>
-    <row r="90" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A90" s="62" t="s">
+      <c r="B92" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="64" t="s">
+      <c r="C92" s="47"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
+      <c r="G92" s="38"/>
+      <c r="H92" s="38"/>
+      <c r="I92" s="38"/>
+      <c r="J92" s="38"/>
+    </row>
+    <row r="93" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A93" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="54"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="54"/>
-      <c r="F90" s="54"/>
-      <c r="G90" s="54"/>
-      <c r="H90" s="54"/>
-      <c r="I90" s="54"/>
-      <c r="J90" s="54"/>
-    </row>
-    <row r="91" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A91" s="62" t="s">
+      <c r="B93" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="63" t="s">
+      <c r="C93" s="47"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38"/>
+      <c r="G93" s="38"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="38"/>
+      <c r="J93" s="38"/>
+    </row>
+    <row r="94" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A94" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="63"/>
-      <c r="D91" s="54"/>
-      <c r="E91" s="54"/>
-      <c r="F91" s="54"/>
-      <c r="G91" s="54"/>
-      <c r="H91" s="54"/>
-      <c r="I91" s="54"/>
-      <c r="J91" s="54"/>
-    </row>
-    <row r="92" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A92" s="62" t="s">
+      <c r="B94" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="B92" s="63" t="s">
+      <c r="C94" s="47"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+      <c r="G94" s="38"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="38"/>
+      <c r="J94" s="38"/>
+    </row>
+    <row r="95" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A95" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C92" s="63"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="54"/>
-      <c r="F92" s="54"/>
-      <c r="G92" s="54"/>
-      <c r="H92" s="54"/>
-      <c r="I92" s="54"/>
-      <c r="J92" s="54"/>
-    </row>
-    <row r="93" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A93" s="62" t="s">
+      <c r="B95" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="63" t="s">
+      <c r="C95" s="47"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="38"/>
+      <c r="G95" s="38"/>
+      <c r="H95" s="38"/>
+      <c r="I95" s="38"/>
+      <c r="J95" s="38"/>
+    </row>
+    <row r="96" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A96" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="C93" s="63"/>
-      <c r="D93" s="54"/>
-      <c r="E93" s="54"/>
-      <c r="F93" s="54"/>
-      <c r="G93" s="54"/>
-      <c r="H93" s="54"/>
-      <c r="I93" s="54"/>
-      <c r="J93" s="54"/>
-    </row>
-    <row r="94" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A94" s="62" t="s">
+      <c r="B96" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="B94" s="63" t="s">
+      <c r="C96" s="47"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="38"/>
+      <c r="G96" s="38"/>
+      <c r="H96" s="38"/>
+      <c r="I96" s="38"/>
+      <c r="J96" s="38"/>
+    </row>
+    <row r="97" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A97" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C94" s="63"/>
-      <c r="D94" s="54"/>
-      <c r="E94" s="54"/>
-      <c r="F94" s="54"/>
-      <c r="G94" s="54"/>
-      <c r="H94" s="54"/>
-      <c r="I94" s="54"/>
-      <c r="J94" s="54"/>
-    </row>
-    <row r="95" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A95" s="62" t="s">
+      <c r="B97" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="B95" s="63" t="s">
+      <c r="C97" s="47"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38"/>
+      <c r="G97" s="38"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="38"/>
+      <c r="J97" s="38"/>
+    </row>
+    <row r="98" ht="14.25" customHeight="1" spans="1:10">
+      <c r="A98" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C95" s="63"/>
-      <c r="D95" s="54"/>
-      <c r="E95" s="54"/>
-      <c r="F95" s="54"/>
-      <c r="G95" s="54"/>
-      <c r="H95" s="54"/>
-      <c r="I95" s="54"/>
-      <c r="J95" s="54"/>
-    </row>
-    <row r="96" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A96" s="62" t="s">
+      <c r="B98" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="B96" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="C96" s="63"/>
-      <c r="D96" s="54"/>
-      <c r="E96" s="54"/>
-      <c r="F96" s="54"/>
-      <c r="G96" s="54"/>
-      <c r="H96" s="54"/>
-      <c r="I96" s="54"/>
-      <c r="J96" s="54"/>
-    </row>
-    <row r="97" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A97" s="62" t="s">
-        <v>103</v>
-      </c>
-      <c r="B97" s="63" t="s">
-        <v>104</v>
-      </c>
-      <c r="C97" s="63"/>
-      <c r="D97" s="54"/>
-      <c r="E97" s="54"/>
-      <c r="F97" s="54"/>
-      <c r="G97" s="54"/>
-      <c r="H97" s="54"/>
-      <c r="I97" s="54"/>
-      <c r="J97" s="54"/>
-    </row>
-    <row r="98" ht="14.25" customHeight="1" spans="1:10">
-      <c r="A98" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="B98" s="63" t="s">
-        <v>106</v>
-      </c>
-      <c r="C98" s="63"/>
-      <c r="D98" s="54"/>
-      <c r="E98" s="54"/>
-      <c r="F98" s="54"/>
-      <c r="G98" s="54"/>
-      <c r="H98" s="54"/>
-      <c r="I98" s="54"/>
-      <c r="J98" s="54"/>
+      <c r="C98" s="47"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38"/>
+      <c r="G98" s="38"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="38"/>
+      <c r="J98" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -3567,7 +3506,7 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:25">
       <c r="A1" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3596,7 +3535,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:25">
       <c r="A2" s="15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -3652,7 +3591,7 @@
     </row>
     <row r="4" ht="13.5" customHeight="1" spans="1:25">
       <c r="A4" s="17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>34</v>
@@ -3691,7 +3630,7 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:25">
       <c r="A5" s="16" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B5" s="18">
         <v>0.1</v>
@@ -3730,7 +3669,7 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:25">
       <c r="A6" s="16" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4463,7 +4402,7 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:25">
       <c r="A23" s="19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B23" s="21">
         <f>SUM(B7:B22)</f>
@@ -4534,7 +4473,7 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:25">
       <c r="A25" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -4563,7 +4502,7 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:25">
       <c r="A26" s="23" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B26" s="23"/>
       <c r="C26" s="23"/>
@@ -4620,13 +4559,13 @@
     <row r="28" ht="16.5" customHeight="1" spans="1:25">
       <c r="A28" s="17"/>
       <c r="B28" s="17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
@@ -4635,7 +4574,7 @@
       <c r="K28" s="25"/>
       <c r="L28" s="25"/>
       <c r="M28" s="25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="N28" s="25"/>
       <c r="O28" s="25"/>
@@ -4654,14 +4593,14 @@
       <c r="A29" s="16"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D29" s="24" t="s">
         <v>39</v>
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="24" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
@@ -4670,7 +4609,7 @@
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
       <c r="M29" s="24" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="N29" s="24" t="s">
         <v>34</v>
@@ -4958,7 +4897,7 @@
     <row r="35" ht="16.5" customHeight="1" spans="1:25">
       <c r="A35" s="16"/>
       <c r="B35" s="24" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C35" s="24">
         <v>100</v>
@@ -5513,7 +5452,7 @@
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:25">
       <c r="A54" s="27" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B54" s="27"/>
       <c r="C54" s="27"/>
@@ -5542,7 +5481,7 @@
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:25">
       <c r="A55" s="27" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B55" s="27"/>
       <c r="C55" s="27"/>
@@ -5571,7 +5510,7 @@
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:25">
       <c r="A56" s="27" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B56" s="27"/>
       <c r="C56" s="27"/>
@@ -5627,7 +5566,7 @@
     </row>
     <row r="58" ht="16.5" customHeight="1" spans="1:25">
       <c r="A58" s="4" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -5656,7 +5595,7 @@
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:25">
       <c r="A59" s="23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B59" s="23"/>
       <c r="C59" s="23"/>
@@ -5685,7 +5624,7 @@
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:25">
       <c r="A60" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -5693,7 +5632,7 @@
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
@@ -5717,7 +5656,7 @@
     <row r="61" ht="16.5" customHeight="1" spans="1:25">
       <c r="A61" s="16"/>
       <c r="B61" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
@@ -5747,18 +5686,18 @@
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="24" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D62" s="24" t="s">
         <v>39</v>
       </c>
       <c r="E62" s="16"/>
       <c r="F62" s="16" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G62" s="16"/>
       <c r="H62" s="24" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I62" s="24">
         <v>0</v>
@@ -6245,7 +6184,7 @@
     <row r="68" ht="16.5" customHeight="1" spans="1:25">
       <c r="A68" s="16"/>
       <c r="B68" s="16" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C68" s="16">
         <v>100</v>
@@ -7161,7 +7100,7 @@
       <c r="E80" s="16"/>
       <c r="F80" s="16"/>
       <c r="G80" s="29" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H80" s="29"/>
       <c r="I80" s="29"/>
@@ -7218,7 +7157,7 @@
       <c r="F82" s="16"/>
       <c r="G82" s="16"/>
       <c r="H82" s="24" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I82" s="24">
         <v>1</v>
@@ -7961,7 +7900,7 @@
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="24" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I99" s="20">
         <f>SUM(I83:I98)</f>
@@ -8025,7 +7964,7 @@
     </row>
     <row r="101" ht="60" customHeight="1" spans="1:25">
       <c r="A101" s="32" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B101" s="20">
         <f ca="1">SUM(M88:M98)</f>
@@ -8093,56 +8032,56 @@
   <sheetData>
     <row r="1" ht="21" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" ht="36.75" customHeight="1" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" ht="17" spans="1:3">
+    <row r="6" ht="34" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -8154,56 +8093,56 @@
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="2"/>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B13" s="6">
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B14" s="7">
         <v>0.075</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B15" s="6">
         <v>3</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -8213,66 +8152,66 @@
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="8" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B18" s="10">
         <f>BINOMDIST($B$15,$B$13,$B$14,FALSE)</f>
         <v>0.00360966796875</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B19" s="11">
         <f>BINOMDIST($B$13,$B$13,$B$14,FALSE)</f>
         <v>2.373046875e-6</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" ht="17" spans="1:3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" ht="34" spans="1:3">
       <c r="A20" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B20" s="10">
         <f>1-BINOMDIST($B$15-1,$B$13,$B$14,TRUE)</f>
         <v>0.00375837890624997</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B21" s="12">
         <f>$B$13*$B$14</f>
         <v>0.375</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="2"/>
@@ -8284,56 +8223,56 @@
     </row>
     <row r="24" ht="17" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="2"/>
     </row>
     <row r="26" ht="17" spans="1:3">
       <c r="A26" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
     <row r="27" ht="17" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B27" s="6">
         <v>5</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" ht="17" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B28" s="7">
         <v>0.04</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" ht="17" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B29" s="6">
         <v>3</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -8343,42 +8282,42 @@
     </row>
     <row r="31" ht="17" spans="1:3">
       <c r="A31" s="8" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" ht="17" spans="1:3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" ht="34" spans="1:3">
       <c r="A32" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B32" s="10">
         <f>1-BINOMDIST($B$29-1,$B$27,$B$28,TRUE)</f>
         <v>0.000602214399999967</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" ht="17" spans="1:3">
       <c r="A33" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B33" s="11">
         <f>1-BINOMDIST(1,$B$27,$B$28,TRUE)</f>
         <v>0.0147579904</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" ht="17" spans="1:3">
       <c r="A34" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B34" s="12">
         <f>$B$27*$B$28</f>
@@ -8393,45 +8332,45 @@
     </row>
     <row r="36" ht="17" spans="1:3">
       <c r="A36" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="2"/>
     </row>
     <row r="38" ht="17" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B38" s="11">
         <f>1-BINOMDIST(2,5,0.05,TRUE)</f>
         <v>0.00115812500000001</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:3">
       <c r="A39" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B39" s="10">
         <f>1-BINOMDIST(2,15,0.05,TRUE)</f>
         <v>0.0362002386427291</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" ht="17" spans="1:3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40" ht="34" spans="1:3">
       <c r="A40" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -8443,28 +8382,28 @@
     </row>
     <row r="42" ht="17" spans="1:3">
       <c r="A42" s="4" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
     </row>
-    <row r="43" ht="17" spans="1:3">
+    <row r="43" ht="34" spans="1:3">
       <c r="A43" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" ht="17" spans="1:3">
+    <row r="45" ht="34" spans="1:3">
       <c r="A45" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -8476,53 +8415,53 @@
     </row>
     <row r="47" ht="17" spans="1:3">
       <c r="A47" s="4" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
     </row>
     <row r="48" ht="17" spans="1:3">
       <c r="A48" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49" ht="17" spans="1:3">
       <c r="A49" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="50" ht="17" spans="1:3">
       <c r="A50" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" ht="17" spans="1:3">
       <c r="A51" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -8532,7 +8471,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="14" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
